--- a/output-submit/促销组合优化建议.xlsx
+++ b/output-submit/促销组合优化建议.xlsx
@@ -2687,7 +2687,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
+    <dataValidation sqref="I2:I200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
       <formula1>"保留,调整,取消"</formula1>
     </dataValidation>
   </dataValidations>
